--- a/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R68c6dc6da2ea4315"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R482509b03761467c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R015d16bfa98f4ecc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3316b7202cb458e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R482509b03761467c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7d5c93a1e10445e2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re3316b7202cb458e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd0cf5e957604d8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7d5c93a1e10445e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rde2f33b37cb84132"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd0cf5e957604d8f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc581826ed1544efc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rde2f33b37cb84132"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5dd1875a5f84e20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc581826ed1544efc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fe3d0ce2e4548be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re5dd1875a5f84e20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra9429ae2687e4aee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fe3d0ce2e4548be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f07f39237164bac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra9429ae2687e4aee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3abb2ec1e3884260"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f07f39237164bac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52dd796c793b46e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3abb2ec1e3884260"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc391182cedf34dc8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52dd796c793b46e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6b2bd037ced409f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Table/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc391182cedf34dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfffd56dc3a344d5e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -92,7 +92,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6b2bd037ced409f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f1324294c9c46ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>